--- a/artfynd/A 48345-2021 artfynd.xlsx
+++ b/artfynd/A 48345-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120481414</v>
+        <v>120481080</v>
       </c>
       <c r="B2" t="n">
-        <v>94704</v>
+        <v>57336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>324317</v>
+        <v>324387</v>
       </c>
       <c r="R2" t="n">
-        <v>6430635</v>
+        <v>6430743</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120481080</v>
+        <v>120481414</v>
       </c>
       <c r="B3" t="n">
-        <v>57336</v>
+        <v>94704</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>324387</v>
+        <v>324317</v>
       </c>
       <c r="R3" t="n">
-        <v>6430743</v>
+        <v>6430635</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 48345-2021 artfynd.xlsx
+++ b/artfynd/A 48345-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120481080</v>
+        <v>120481414</v>
       </c>
       <c r="B2" t="n">
-        <v>57336</v>
+        <v>94704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>324387</v>
+        <v>324317</v>
       </c>
       <c r="R2" t="n">
-        <v>6430743</v>
+        <v>6430635</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120481414</v>
+        <v>120481080</v>
       </c>
       <c r="B3" t="n">
-        <v>94704</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>324317</v>
+        <v>324387</v>
       </c>
       <c r="R3" t="n">
-        <v>6430635</v>
+        <v>6430743</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 48345-2021 artfynd.xlsx
+++ b/artfynd/A 48345-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120481080</v>
+        <v>120481414</v>
       </c>
       <c r="B2" t="n">
-        <v>57363</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>324387</v>
+        <v>324317</v>
       </c>
       <c r="R2" t="n">
-        <v>6430743</v>
+        <v>6430635</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120481414</v>
+        <v>120481080</v>
       </c>
       <c r="B3" t="n">
-        <v>94818</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>324317</v>
+        <v>324387</v>
       </c>
       <c r="R3" t="n">
-        <v>6430635</v>
+        <v>6430743</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,6 +886,112 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>115628667</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skogssäter-Stenungsund-Ingelkärr, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>324443</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6430643</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sandra Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sandra Johansson, Robert Petersen, Johanna Ek, Tilda Lindkvist, Jeanette Karlsson, Mathias Molau</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48345-2021 artfynd.xlsx
+++ b/artfynd/A 48345-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120481414</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120481080</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,8 +1007,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115628667</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>